--- a/src/main/resources/excel/0 - Vocabulary.xlsx
+++ b/src/main/resources/excel/0 - Vocabulary.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Ordinal Numbers" sheetId="1" state="visible" r:id="rId3"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="927">
   <si>
     <t xml:space="preserve">First</t>
   </si>
@@ -3081,7 +3081,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3090,16 +3090,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -3870,7 +3866,7 @@
       <c r="B1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="I1" s="4" t="b">
+      <c r="I1" s="2" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -4644,9 +4640,9 @@
   <dimension ref="A1:F91"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="25.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="29.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="3" style="4" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="25.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="29.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="3" style="2" width="11.52"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1026" style="2" width="8.68"/>
   </cols>
   <sheetData>
@@ -4654,27 +4650,24 @@
       <c r="A1" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4682,13 +4675,13 @@
       <c r="A3" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4696,1219 +4689,1219 @@
       <c r="A4" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="2" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="2" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F45" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F48" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="F49" s="4" t="s">
+      <c r="F49" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="F50" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="F51" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="F52" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="F53" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="F54" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D55" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="F55" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D56" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="F56" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="F57" s="4" t="s">
+      <c r="F57" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="F58" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="F59" s="4" t="s">
+      <c r="F59" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D60" s="2" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="F61" s="4" t="s">
+      <c r="F61" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="F62" s="4" t="s">
+      <c r="F62" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="F63" s="4" t="s">
+      <c r="F63" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="F64" s="4" t="s">
+      <c r="F64" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="D65" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="F65" s="4" t="s">
+      <c r="F65" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D66" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="F66" s="4" t="s">
+      <c r="F66" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D67" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="F67" s="4" t="s">
+      <c r="F67" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="F68" s="4" t="s">
+      <c r="F68" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D69" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="F69" s="4" t="s">
+      <c r="F69" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4" t="s">
+      <c r="A70" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D70" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="F70" s="4" t="s">
+      <c r="F70" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="s">
+      <c r="A71" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D71" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="F71" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="D72" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="F72" s="4" t="s">
+      <c r="F72" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="4" t="s">
+      <c r="A73" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="D73" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="F73" s="4" t="s">
+      <c r="F73" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="F74" s="4" t="s">
+      <c r="F74" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="s">
+      <c r="A75" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="D75" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="F75" s="4" t="s">
+      <c r="F75" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="D76" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="F76" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="s">
+      <c r="A77" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="D77" s="4" t="s">
+      <c r="D77" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="F77" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="s">
+      <c r="A78" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="D78" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="F78" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="4" t="s">
+      <c r="A79" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B79" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="D79" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="F79" s="4" t="s">
+      <c r="F79" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="4" t="s">
+      <c r="A80" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B80" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="D80" s="4" t="s">
+      <c r="D80" s="2" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="4" t="s">
+      <c r="A81" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="B81" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="D81" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="F81" s="4" t="s">
+      <c r="F81" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="4" t="s">
+      <c r="A82" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="B82" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="D82" s="4" t="s">
+      <c r="D82" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="F82" s="4" t="s">
+      <c r="F82" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="4" t="s">
+      <c r="A83" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B83" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="D83" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="F83" s="4" t="s">
+      <c r="F83" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="4" t="s">
+      <c r="A84" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B84" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="D84" s="4" t="s">
+      <c r="D84" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="F84" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="4" t="s">
+      <c r="A85" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="D85" s="4" t="s">
+      <c r="D85" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="F85" s="4" t="s">
+      <c r="F85" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="4" t="s">
+      <c r="A86" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="D86" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="F86" s="4" t="s">
+      <c r="F86" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="4" t="s">
+      <c r="A87" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B87" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="D87" s="4" t="s">
+      <c r="D87" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="F87" s="4" t="s">
+      <c r="F87" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="4" t="s">
+      <c r="A88" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="B88" s="4" t="s">
+      <c r="B88" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="D88" s="4" t="s">
+      <c r="D88" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="F88" s="4" t="s">
+      <c r="F88" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="4" t="s">
+      <c r="A89" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B89" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="D89" s="4" t="s">
+      <c r="D89" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="F89" s="4" t="s">
+      <c r="F89" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="4" t="s">
+      <c r="A90" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B90" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="D90" s="4" t="s">
+      <c r="D90" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="F90" s="4" t="s">
+      <c r="F90" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="4" t="s">
+      <c r="A91" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="D91" s="4" t="s">
+      <c r="D91" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="F91" s="4" t="s">
+      <c r="F91" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -7411,7 +7404,7 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="4" t="s">
         <v>216</v>
       </c>
       <c r="B54" s="1" t="s">
@@ -7425,7 +7418,7 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5" t="s">
+      <c r="A55" s="4" t="s">
         <v>219</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -7439,7 +7432,7 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="4" t="s">
         <v>222</v>
       </c>
       <c r="B56" s="1" t="s">
@@ -7453,7 +7446,7 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5" t="s">
+      <c r="A57" s="4" t="s">
         <v>225</v>
       </c>
       <c r="B57" s="1" t="s">
@@ -7467,7 +7460,7 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="4" t="s">
         <v>228</v>
       </c>
       <c r="B58" s="1" t="s">
@@ -7481,7 +7474,7 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="5" t="s">
+      <c r="A59" s="4" t="s">
         <v>231</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -7495,7 +7488,7 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="5" t="s">
+      <c r="A60" s="4" t="s">
         <v>234</v>
       </c>
       <c r="B60" s="1" t="s">
@@ -7506,7 +7499,7 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="4" t="s">
         <v>237</v>
       </c>
       <c r="B61" s="1" t="s">
@@ -7520,7 +7513,7 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="4" t="s">
         <v>240</v>
       </c>
       <c r="B62" s="1" t="s">
@@ -7534,7 +7527,7 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="4" t="s">
         <v>243</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -7548,7 +7541,7 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="5" t="s">
+      <c r="A64" s="4" t="s">
         <v>246</v>
       </c>
       <c r="B64" s="1" t="s">
@@ -7562,7 +7555,7 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="5" t="s">
+      <c r="A65" s="4" t="s">
         <v>249</v>
       </c>
       <c r="B65" s="1" t="s">
@@ -7576,13 +7569,13 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="5" t="s">
+      <c r="A66" s="4" t="s">
         <v>853</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D66" s="2" t="s">
         <v>855</v>
       </c>
       <c r="F66" s="1" t="s">
@@ -7590,13 +7583,13 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="5" t="s">
+      <c r="A67" s="4" t="s">
         <v>856</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="2" t="s">
         <v>857</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D67" s="2" t="s">
         <v>858</v>
       </c>
       <c r="F67" s="1" t="s">
@@ -7604,13 +7597,13 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="5" t="s">
+      <c r="A68" s="4" t="s">
         <v>859</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="2" t="s">
         <v>860</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" s="2" t="s">
         <v>861</v>
       </c>
       <c r="F68" s="1" t="s">
@@ -7618,13 +7611,13 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="5" t="s">
+      <c r="A69" s="4" t="s">
         <v>862</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="2" t="s">
         <v>863</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D69" s="2" t="s">
         <v>864</v>
       </c>
       <c r="F69" s="1" t="s">
@@ -7632,13 +7625,13 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="5" t="s">
+      <c r="A70" s="4" t="s">
         <v>865</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="2" t="s">
         <v>866</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D70" s="2" t="s">
         <v>867</v>
       </c>
       <c r="F70" s="1" t="s">
@@ -7646,13 +7639,13 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="5" t="s">
+      <c r="A71" s="4" t="s">
         <v>868</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="2" t="s">
         <v>869</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D71" s="2" t="s">
         <v>870</v>
       </c>
       <c r="F71" s="1" t="s">
@@ -7660,13 +7653,13 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="5" t="s">
+      <c r="A72" s="4" t="s">
         <v>871</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="2" t="s">
         <v>872</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="D72" s="2" t="s">
         <v>873</v>
       </c>
       <c r="F72" s="1" t="s">
@@ -7696,10 +7689,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>874</v>
       </c>
       <c r="D1" s="3" t="s">
@@ -7707,366 +7700,366 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>876</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>876</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>877</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>878</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>878</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>879</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>880</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>880</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>881</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>882</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>882</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>883</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>884</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>884</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>885</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>886</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>886</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>887</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="2" t="s">
         <v>888</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>888</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>889</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>890</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>891</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="2" t="s">
         <v>892</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="2" t="s">
         <v>892</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>893</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>894</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>895</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="2" t="s">
         <v>896</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>897</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>898</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>899</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="2" t="s">
         <v>900</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="2" t="s">
         <v>900</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>899</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="2" t="s">
         <v>901</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>901</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>902</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="2" t="s">
         <v>903</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="2" t="s">
         <v>903</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>904</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="2" t="s">
         <v>905</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>905</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>906</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="2" t="s">
         <v>907</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="2" t="s">
         <v>907</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>908</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="2" t="s">
         <v>909</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>909</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>910</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="2" t="s">
         <v>911</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="2" t="s">
         <v>911</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>912</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="2" t="s">
         <v>913</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="2" t="s">
         <v>913</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>914</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="2" t="s">
         <v>915</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="2" t="s">
         <v>915</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>916</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="2" t="s">
         <v>917</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="2" t="s">
         <v>917</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>918</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="2" t="s">
         <v>919</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="2" t="s">
         <v>919</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>920</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="2" t="s">
         <v>921</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="2" t="s">
         <v>921</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>922</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="2" t="s">
         <v>923</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="2" t="s">
         <v>923</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>924</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -8093,10 +8086,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>874</v>
       </c>
       <c r="D1" s="3" t="s">
@@ -8104,58 +8097,58 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>882</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>882</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>883</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>925</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="2" t="s">
         <v>925</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>901</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>901</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>902</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="2" t="s">
         <v>925</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>913</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>913</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>926</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="2" t="s">
         <v>925</v>
       </c>
     </row>

--- a/src/main/resources/excel/0 - Vocabulary.xlsx
+++ b/src/main/resources/excel/0 - Vocabulary.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Ordinal Numbers" sheetId="1" state="visible" r:id="rId3"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="942">
   <si>
     <t xml:space="preserve">First</t>
   </si>
@@ -2094,6 +2094,162 @@
     <t xml:space="preserve">ˈfɪŋɡərz</t>
   </si>
   <si>
+    <t xml:space="preserve">Palm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">palma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pɑm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armpit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈɑrmˌpɪt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nipple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pezón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈnɪpəl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buttock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nalga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈbʌtək</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planta del pie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soʊl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empeine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Face</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feɪs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nostril</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fosa nasal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈnɑstrɪl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Earlobe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lóbulo de la oreja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fingernail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uña</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈfɪŋɡərˌneɪl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thumb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pulgar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">θʌm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Index Finder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Índice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈɪndɛks ˈfaɪndər</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Middle Finger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dedo medio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈmɪdəl ˈfɪŋɡər</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ring Finger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dedo anular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rɪŋ ˈfɪŋɡər</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small Finger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dedo meñique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smɔl ˈfɪŋɡər</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tibia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ʃɪn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pecho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brɛst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toenail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uña del pie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈtoʊˌneɪl</t>
+  </si>
+  <si>
     <t xml:space="preserve">Finger</t>
   </si>
   <si>
@@ -2292,9 +2448,6 @@
     <t xml:space="preserve">ɪnˈtɛstənz</t>
   </si>
   <si>
-    <t xml:space="preserve">Earlobe</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lóbulo</t>
   </si>
   <si>
@@ -2484,15 +2637,9 @@
     <t xml:space="preserve">blʌd</t>
   </si>
   <si>
-    <t xml:space="preserve">Breast</t>
-  </si>
-  <si>
     <t xml:space="preserve">Seno</t>
   </si>
   <si>
-    <t xml:space="preserve">brɛst</t>
-  </si>
-  <si>
     <t xml:space="preserve">Breasts</t>
   </si>
   <si>
@@ -2523,9 +2670,6 @@
     <t xml:space="preserve">Nail</t>
   </si>
   <si>
-    <t xml:space="preserve">Uña</t>
-  </si>
-  <si>
     <t xml:space="preserve">neɪl</t>
   </si>
   <si>
@@ -2551,105 +2695,6 @@
   </si>
   <si>
     <t xml:space="preserve">veɪnz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Febrero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marzo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abril</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puede</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agosto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Septiembre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Octubre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noviembre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diciembre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monday</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈmʌnˌdeɪ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tuesday</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈtuzˌdeɪ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wednesday</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miércoles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈwɛnzˌdeɪ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thursday</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jueves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈθɜrzˌdeɪ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Friday</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viernes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈfraɪˌdeɪ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saturday</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sábado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈsætərˌdeɪ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunday</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Domingo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈsʌnˌdeɪ</t>
   </si>
   <si>
     <t xml:space="preserve">A</t>
@@ -2815,11 +2860,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2926,6 +2970,14 @@
     <font>
       <sz val="10"/>
       <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -3081,7 +3133,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3098,7 +3150,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3189,6 +3253,1992 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>12600</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>97560</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>317880</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>2897640</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="Image 1" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7565400" y="53328240"/>
+          <a:ext cx="4390920" cy="2800080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3095640</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>2609640</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Image 2" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="56426040"/>
+          <a:ext cx="3095640" cy="2609640"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>118080</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>2209680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 3" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="34842600"/>
+          <a:ext cx="3390840" cy="2209680"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>241920</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>2381040</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image 4" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="70072200"/>
+          <a:ext cx="3514680" cy="2381040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>270360</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>2781000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Image 5" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="72654840"/>
+          <a:ext cx="3543120" cy="2781000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3228840</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>2104920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Image 6" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="75616560"/>
+          <a:ext cx="3228840" cy="2104920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2266560</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>2285640</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Image 9" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="37282680"/>
+          <a:ext cx="2266560" cy="2285640"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>79920</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>2238120</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Image 11" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="77891040"/>
+          <a:ext cx="3352680" cy="2238120"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>289440</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>2161800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Image 13" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId9"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="67435560"/>
+          <a:ext cx="3562200" cy="2161800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2085840</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>2114280</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Image 14" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId10"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="47510640"/>
+          <a:ext cx="2085840" cy="2114280"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2514240</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>2352600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Image 15" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId11"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="39734640"/>
+          <a:ext cx="2514240" cy="2352600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2638080</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>2438280</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Image 16" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="59198040"/>
+          <a:ext cx="2638080" cy="2438280"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3209760</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>2104920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Image 18" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId13"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="45248040"/>
+          <a:ext cx="3209760" cy="2104920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2095200</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>2209680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Image 19" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId14"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="50284440"/>
+          <a:ext cx="2095200" cy="2209680"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1399680</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>2371680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Image 20" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId15"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="80307360"/>
+          <a:ext cx="1399680" cy="2371680"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2952720</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>2419200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Image 21" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId16"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="82854000"/>
+          <a:ext cx="2952720" cy="2419200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2781000</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>2428560</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Image 22" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId17"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="42515280"/>
+          <a:ext cx="2781000" cy="2428560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2104920</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>2333520</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Image 23" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId18"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="32275080"/>
+          <a:ext cx="2104920" cy="2333520"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2543040</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>2447640</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Image 24" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId19"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="0"/>
+          <a:ext cx="2543040" cy="2447640"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2238120</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>2114280</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Image 25" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId20"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="85330080"/>
+          <a:ext cx="2238120" cy="2114280"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2771640</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>2238120</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Image 26" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId21"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="29802600"/>
+          <a:ext cx="2771640" cy="2238120"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2781000</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>2152440</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Image 27" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId22"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="11290320"/>
+          <a:ext cx="2781000" cy="2152440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2724120</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>2495520</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Image 28" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId23"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="26883360"/>
+          <a:ext cx="2724120" cy="2495520"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3133800</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>2114280</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="Image 29" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId24"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="4059720"/>
+          <a:ext cx="3133800" cy="2114280"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>232560</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>2057040</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Image 30" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId25"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="22092120"/>
+          <a:ext cx="3505320" cy="2057040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3162240</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>2199960</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="Image 31" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId26"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="24387120"/>
+          <a:ext cx="3162240" cy="2199960"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2666880</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>2314440</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="Image 32" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId27"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="19628640"/>
+          <a:ext cx="2666880" cy="2314440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2352600</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1304640</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="Image 33" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId28"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="2511360"/>
+          <a:ext cx="2352600" cy="1304640"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2685960</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1028160</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="Image 34" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId29"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="17944560"/>
+          <a:ext cx="2685960" cy="1028160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2161800</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>2161800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="29" name="Image 35" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId30"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="9039960"/>
+          <a:ext cx="2161800" cy="2161800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2133360</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>2695320</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="30" name="Image 36" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId31"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="87592680"/>
+          <a:ext cx="2133360" cy="2695320"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2257200</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>2390400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="31" name="Image 37" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId32"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="6401520"/>
+          <a:ext cx="2257200" cy="2390400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2923920</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>2333520</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="32" name="Image 38" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId33"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="90376200"/>
+          <a:ext cx="2923920" cy="2333520"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3257640</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>2314440</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="33" name="Image 40" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId34"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="92852280"/>
+          <a:ext cx="3257640" cy="2314440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2857320</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>2047680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="Image 42" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId35"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="95268240"/>
+          <a:ext cx="2857320" cy="2047680"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1981080</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>2571480</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="35" name="Image 43" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId36"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="97483320"/>
+          <a:ext cx="1981080" cy="2571480"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1866600</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>2323800</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="36" name="Image 44" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId37"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="100195920"/>
+          <a:ext cx="1866600" cy="2323800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2161800</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>2676240</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="37" name="Image 45" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId38"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="102718800"/>
+          <a:ext cx="2161800" cy="2676240"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2180880</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>2333520</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="Image 46" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId39"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="105549840"/>
+          <a:ext cx="2180880" cy="2333520"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2714400</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>2314440</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="39" name="Image 47" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId40"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="13588200"/>
+          <a:ext cx="2714400" cy="2314440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>575280</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>1495080</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="40" name="Image 48" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId41"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="16099920"/>
+          <a:ext cx="3848040" cy="1495080"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3152520</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>2590560</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="41" name="Image 49" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId42"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="108096840"/>
+          <a:ext cx="3152520" cy="2590560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>270360</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>2171520</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="42" name="Image 50" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId43"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="110773800"/>
+          <a:ext cx="3543120" cy="2171520"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2381040</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>2476440</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="43" name="Image 51" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId44"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="62057880"/>
+          <a:ext cx="2381040" cy="2476440"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2990880</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>2304720</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="44" name="Image 52" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId45"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7552800" y="113036400"/>
+          <a:ext cx="2990880" cy="2304720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>161640</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>2523960</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="45" name="Image 7" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6502320" y="16544160"/>
+          <a:ext cx="2600280" cy="2523960"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>275760</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>2266560</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="46" name="Image 8" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6502320" y="14036040"/>
+          <a:ext cx="2714400" cy="2266560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>450360</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>2285640</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="47" name="Image 10" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6502320" y="6769800"/>
+          <a:ext cx="2076120" cy="2285640"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>304560</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>2104920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="48" name="Image 12" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6502320" y="3173040"/>
+          <a:ext cx="2743200" cy="2104920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>266400</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>2514240</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="49" name="Image 17" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6502320" y="19443240"/>
+          <a:ext cx="2705040" cy="2514240"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>723600</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>2400120</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="50" name="Image 39" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6502320" y="0"/>
+          <a:ext cx="3162240" cy="2400120"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>676080</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>1904760</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="Image 41" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6502320" y="12093480"/>
+          <a:ext cx="3114720" cy="1904760"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5921,731 +7971,1510 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:M70"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="26.43"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="3" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="46.43"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="2" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="197.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="109.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="171.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="177.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="180.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="197.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="132.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="94.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" customFormat="false" ht="194" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" customFormat="false" ht="167.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" customFormat="false" ht="183.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" customFormat="false" ht="204.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" customFormat="false" ht="181.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" customFormat="false" ht="189.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" customFormat="false" ht="192.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" customFormat="false" ht="193.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" customFormat="false" ht="206.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" customFormat="false" ht="202.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" customFormat="false" ht="178.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="F35" s="1"/>
+    </row>
+    <row r="36" customFormat="false" ht="180" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="F37" s="1"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="F38" s="1"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="F39" s="1"/>
+    </row>
+    <row r="40" customFormat="false" ht="179.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="F41" s="1"/>
+    </row>
+    <row r="42" customFormat="false" ht="40.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="F42" s="1"/>
+    </row>
+    <row r="43" customFormat="false" ht="238.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="C43" s="5"/>
+      <c r="D43" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="E43" s="5"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="F44" s="1"/>
+    </row>
+    <row r="45" customFormat="false" ht="218.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="C45" s="5"/>
+      <c r="D45" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="E45" s="5"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+    </row>
+    <row r="46" customFormat="false" ht="199.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="F46" s="1"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="F47" s="1"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="F48" s="1"/>
+    </row>
+    <row r="49" customFormat="false" ht="199.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="F49" s="1"/>
+    </row>
+    <row r="50" customFormat="false" ht="223.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="F50" s="1"/>
+    </row>
+    <row r="51" customFormat="false" ht="183.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="F51" s="1"/>
+    </row>
+    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="F52" s="1"/>
+    </row>
+    <row r="53" customFormat="false" ht="203.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>690</v>
+      </c>
+      <c r="F53" s="1"/>
+    </row>
+    <row r="54" customFormat="false" ht="233.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="179.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="190.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="200.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="178.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="219.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="194.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="190.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="174.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="213.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="198.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="222.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="200.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="210.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="178.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="191.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D53" r:id="rId1" location="" display="pɑm"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="2" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="198.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>534</v>
+        <v>740</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>535</v>
+        <v>741</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>536</v>
+        <v>742</v>
       </c>
       <c r="F1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>537</v>
+        <v>743</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>538</v>
+        <v>744</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>745</v>
+      </c>
+      <c r="F2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>540</v>
+        <v>746</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>541</v>
+        <v>747</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="F3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>543</v>
+        <v>749</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>544</v>
+        <v>750</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="F4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>546</v>
+        <v>752</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>547</v>
+        <v>753</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>754</v>
+      </c>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="169.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>549</v>
+        <v>755</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>550</v>
+        <v>756</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>757</v>
+      </c>
+      <c r="F6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>552</v>
+        <v>758</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>553</v>
+        <v>759</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>554</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>760</v>
+      </c>
+      <c r="F7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>555</v>
+        <v>761</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>556</v>
+        <v>762</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>763</v>
+      </c>
+      <c r="F8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>558</v>
+        <v>764</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>559</v>
+        <v>765</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>766</v>
+      </c>
+      <c r="F9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>561</v>
+        <v>767</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>562</v>
+        <v>768</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="F10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>564</v>
+        <v>770</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>565</v>
+        <v>771</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>772</v>
+      </c>
+      <c r="F11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>567</v>
+        <v>773</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>568</v>
+        <v>774</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>775</v>
+      </c>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>570</v>
+        <v>776</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>571</v>
+        <v>777</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>572</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>778</v>
+      </c>
+      <c r="F13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>573</v>
+        <v>779</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>571</v>
+        <v>780</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>781</v>
+      </c>
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" customFormat="false" ht="192.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>575</v>
+        <v>782</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>576</v>
+        <v>783</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>784</v>
+      </c>
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>578</v>
+        <v>785</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>579</v>
+        <v>786</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>787</v>
+      </c>
+      <c r="F16" s="1"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>581</v>
+        <v>788</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>582</v>
+        <v>789</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>790</v>
+      </c>
+      <c r="F17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>584</v>
+        <v>791</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>585</v>
+        <v>792</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>793</v>
+      </c>
+      <c r="F18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>587</v>
+        <v>794</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>588</v>
+        <v>795</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>796</v>
+      </c>
+      <c r="F19" s="1"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>590</v>
+        <v>797</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>591</v>
+        <v>798</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>592</v>
+        <v>799</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>593</v>
+        <v>800</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>594</v>
+        <v>801</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>802</v>
+      </c>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>596</v>
+        <v>803</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>597</v>
+        <v>804</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>805</v>
+      </c>
+      <c r="F22" s="1"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>599</v>
+        <v>711</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>600</v>
+        <v>806</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>711</v>
+      </c>
+      <c r="F23" s="1"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>602</v>
+        <v>807</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>603</v>
+        <v>808</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>807</v>
+      </c>
+      <c r="F24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>605</v>
+        <v>809</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>606</v>
+        <v>810</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>811</v>
+      </c>
+      <c r="F25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>608</v>
+        <v>812</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>609</v>
+        <v>813</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>610</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>814</v>
+      </c>
+      <c r="F26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>611</v>
+        <v>815</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>612</v>
+        <v>816</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>817</v>
+      </c>
+      <c r="F27" s="1"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>614</v>
+        <v>818</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>615</v>
+        <v>819</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>820</v>
+      </c>
+      <c r="F28" s="1"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>617</v>
+        <v>821</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>618</v>
+        <v>822</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>823</v>
+      </c>
+      <c r="F29" s="1"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>620</v>
+        <v>824</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>621</v>
+        <v>825</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>826</v>
+      </c>
+      <c r="F30" s="1"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>623</v>
+        <v>827</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>624</v>
+        <v>828</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>625</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>829</v>
+      </c>
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" customFormat="false" ht="152.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>626</v>
+        <v>830</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>627</v>
+        <v>831</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>628</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>832</v>
+      </c>
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" customFormat="false" ht="184.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>629</v>
+        <v>833</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>630</v>
+        <v>834</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>835</v>
+      </c>
+      <c r="F33" s="1"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>632</v>
+        <v>836</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>633</v>
+        <v>834</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>634</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>836</v>
+      </c>
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" customFormat="false" ht="215.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>635</v>
+        <v>837</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>636</v>
+        <v>834</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>637</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>838</v>
+      </c>
+      <c r="F35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>638</v>
+        <v>839</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>639</v>
+        <v>840</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>841</v>
+      </c>
+      <c r="F36" s="1"/>
+    </row>
+    <row r="37" customFormat="false" ht="208.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>641</v>
+        <v>842</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>642</v>
+        <v>843</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>844</v>
+      </c>
+      <c r="F37" s="1"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>644</v>
+        <v>845</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>645</v>
+        <v>846</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>847</v>
+      </c>
+      <c r="F38" s="1"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>647</v>
+        <v>848</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>648</v>
+        <v>849</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>850</v>
+      </c>
+      <c r="F39" s="1"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>650</v>
+        <v>851</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>651</v>
+        <v>852</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>652</v>
+        <v>853</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>653</v>
+        <v>854</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>654</v>
+        <v>855</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>655</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>856</v>
+      </c>
+      <c r="F41" s="1"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>656</v>
+        <v>857</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>657</v>
+        <v>858</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>658</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>859</v>
+      </c>
+      <c r="F42" s="1"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>659</v>
+        <v>860</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>660</v>
+        <v>861</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>862</v>
+      </c>
+      <c r="F43" s="1"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>662</v>
+        <v>863</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>663</v>
+        <v>864</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>865</v>
+      </c>
+      <c r="F44" s="1"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>665</v>
+        <v>866</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>666</v>
+        <v>867</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>868</v>
+      </c>
+      <c r="F45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>668</v>
+        <v>734</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>669</v>
+        <v>869</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>736</v>
+      </c>
+      <c r="F46" s="1"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>671</v>
+        <v>870</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>669</v>
+        <v>871</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>672</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>872</v>
+      </c>
+      <c r="F47" s="1"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>673</v>
+        <v>873</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>674</v>
+        <v>874</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>675</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>875</v>
+      </c>
+      <c r="F48" s="1"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>676</v>
+        <v>876</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>677</v>
+        <v>877</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>878</v>
+      </c>
+      <c r="F49" s="1"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>679</v>
+        <v>879</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>680</v>
+        <v>714</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>681</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>880</v>
+      </c>
+      <c r="F50" s="1"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>682</v>
+        <v>881</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>683</v>
+        <v>881</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>882</v>
+      </c>
+      <c r="F51" s="1"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>685</v>
+        <v>883</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>686</v>
+        <v>884</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>687</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>885</v>
+      </c>
+      <c r="F52" s="1"/>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>888</v>
+      </c>
+      <c r="F53" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6655,1025 +9484,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:F72"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="2" width="11.53"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>688</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>689</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>690</v>
-      </c>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>691</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>693</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>694</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>695</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>696</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>697</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>698</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>699</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>700</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>701</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>704</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>705</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>706</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>707</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>708</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>709</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>711</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>712</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>714</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>715</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>716</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>717</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>718</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>719</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>720</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>721</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>722</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>723</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>724</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>725</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>726</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
-        <v>727</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>729</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>730</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>731</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>732</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
-        <v>733</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>734</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>735</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>737</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>738</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>739</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>740</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>741</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>742</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>743</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>744</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>746</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>749</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>753</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>757</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
-        <v>758</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>759</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>760</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>763</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
-        <v>764</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
-        <v>767</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>768</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
-        <v>770</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>771</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
-        <v>773</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>778</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
-        <v>782</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>783</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>784</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
-        <v>785</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>783</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>785</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
-        <v>786</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>783</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
-        <v>788</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>789</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>790</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="s">
-        <v>791</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>793</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="s">
-        <v>794</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>795</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>796</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="s">
-        <v>797</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>799</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>801</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="s">
-        <v>803</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>805</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
-        <v>806</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>807</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>810</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>811</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>813</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>814</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3" t="s">
-        <v>815</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>816</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>817</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="s">
-        <v>818</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>819</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>820</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="s">
-        <v>821</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="s">
-        <v>824</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>825</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>826</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="s">
-        <v>827</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>828</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>829</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="s">
-        <v>830</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>831</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>832</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="s">
-        <v>833</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>833</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>834</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="s">
-        <v>835</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>836</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>837</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="3" t="s">
-        <v>838</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>839</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>840</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>841</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>842</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>843</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>844</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>845</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>846</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>847</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>848</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>849</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>850</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>851</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>852</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="s">
-        <v>853</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>854</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>855</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="s">
-        <v>856</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>857</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>858</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="s">
-        <v>859</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>860</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>861</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="s">
-        <v>862</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>863</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>864</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4" t="s">
-        <v>865</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>866</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>867</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="s">
-        <v>868</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>869</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>870</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="4" t="s">
-        <v>871</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>872</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>873</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7690,24 +9501,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>874</v>
+        <v>889</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>874</v>
+        <v>889</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>875</v>
+        <v>890</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>876</v>
+        <v>891</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>876</v>
+        <v>891</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>877</v>
+        <v>892</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>6</v>
@@ -7715,13 +9526,13 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>6</v>
@@ -7729,13 +9540,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>880</v>
+        <v>895</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>880</v>
+        <v>895</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>881</v>
+        <v>896</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>6</v>
@@ -7743,13 +9554,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>882</v>
+        <v>897</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>882</v>
+        <v>897</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>883</v>
+        <v>898</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>6</v>
@@ -7757,13 +9568,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>884</v>
+        <v>899</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>884</v>
+        <v>899</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>885</v>
+        <v>900</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>6</v>
@@ -7771,13 +9582,13 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>886</v>
+        <v>901</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>886</v>
+        <v>901</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>887</v>
+        <v>902</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>6</v>
@@ -7785,13 +9596,13 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>888</v>
+        <v>903</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>888</v>
+        <v>903</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>889</v>
+        <v>904</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>6</v>
@@ -7813,13 +9624,13 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>890</v>
+        <v>905</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>890</v>
+        <v>905</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>891</v>
+        <v>906</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>6</v>
@@ -7827,13 +9638,13 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>892</v>
+        <v>907</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>892</v>
+        <v>907</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>893</v>
+        <v>908</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>6</v>
@@ -7841,13 +9652,13 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>894</v>
+        <v>909</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>894</v>
+        <v>909</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>895</v>
+        <v>910</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>6</v>
@@ -7855,13 +9666,13 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>896</v>
+        <v>911</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>896</v>
+        <v>911</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>897</v>
+        <v>912</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>6</v>
@@ -7869,13 +9680,13 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>898</v>
+        <v>913</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>898</v>
+        <v>913</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>899</v>
+        <v>914</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>6</v>
@@ -7883,13 +9694,13 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>900</v>
+        <v>915</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>899</v>
+        <v>914</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>6</v>
@@ -7897,13 +9708,13 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>902</v>
+        <v>917</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>6</v>
@@ -7911,13 +9722,13 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>903</v>
+        <v>918</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>903</v>
+        <v>918</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>904</v>
+        <v>919</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>6</v>
@@ -7925,13 +9736,13 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>905</v>
+        <v>920</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>905</v>
+        <v>920</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>906</v>
+        <v>921</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>6</v>
@@ -7939,13 +9750,13 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>907</v>
+        <v>922</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>907</v>
+        <v>922</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>908</v>
+        <v>923</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>6</v>
@@ -7953,13 +9764,13 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>909</v>
+        <v>924</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>909</v>
+        <v>924</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>910</v>
+        <v>925</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>6</v>
@@ -7967,13 +9778,13 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>911</v>
+        <v>926</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>911</v>
+        <v>926</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>912</v>
+        <v>927</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>6</v>
@@ -7981,13 +9792,13 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>913</v>
+        <v>928</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>913</v>
+        <v>928</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>914</v>
+        <v>929</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>6</v>
@@ -7995,13 +9806,13 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>915</v>
+        <v>930</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>915</v>
+        <v>930</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>916</v>
+        <v>931</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>6</v>
@@ -8009,13 +9820,13 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>917</v>
+        <v>932</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>917</v>
+        <v>932</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>918</v>
+        <v>933</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>6</v>
@@ -8023,13 +9834,13 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>919</v>
+        <v>934</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>919</v>
+        <v>934</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>920</v>
+        <v>935</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>6</v>
@@ -8037,13 +9848,13 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>921</v>
+        <v>936</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>921</v>
+        <v>936</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>922</v>
+        <v>937</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>6</v>
@@ -8051,13 +9862,13 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>923</v>
+        <v>938</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>923</v>
+        <v>938</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>924</v>
+        <v>939</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>6</v>
@@ -8087,27 +9898,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>874</v>
+        <v>889</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>874</v>
+        <v>889</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>875</v>
+        <v>890</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>882</v>
+        <v>897</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>882</v>
+        <v>897</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>883</v>
+        <v>898</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>925</v>
+        <v>940</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8121,35 +9932,35 @@
         <v>539</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>925</v>
+        <v>940</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>901</v>
+        <v>916</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>902</v>
+        <v>917</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>925</v>
+        <v>940</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>913</v>
+        <v>928</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>913</v>
+        <v>928</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>926</v>
+        <v>941</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>925</v>
+        <v>940</v>
       </c>
     </row>
   </sheetData>
